--- a/Result/profitability/5236.xlsx
+++ b/Result/profitability/5236.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM46"/>
+  <dimension ref="A1:AM47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.92</v>
       </c>
       <c r="M2" t="n">
-        <v>2.245</v>
+        <v>2.30375</v>
       </c>
       <c r="N2" t="n">
-        <v>55.16625</v>
+        <v>55.24625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.8</v>
       </c>
       <c r="M3" t="n">
-        <v>2.0425</v>
+        <v>2.1525</v>
       </c>
       <c r="N3" t="n">
-        <v>52.0875</v>
+        <v>52.56125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -6272,6 +6272,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>580</v>
+      </c>
+      <c r="D47" t="n">
+        <v>235</v>
+      </c>
+      <c r="E47" t="n">
+        <v>345</v>
+      </c>
+      <c r="F47" t="n">
+        <v>59.52</v>
+      </c>
+      <c r="G47" t="n">
+        <v>182</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>31.33%</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>8</v>
+      </c>
+      <c r="J47" t="n">
+        <v>190</v>
+      </c>
+      <c r="K47" t="n">
+        <v>173</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2.36625</v>
+      </c>
+      <c r="N47" t="n">
+        <v>58.38625</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W47" t="n">
+        <v>-0.08000000000000007</v>
+      </c>
+      <c r="X47" t="n">
+        <v>-0.02693602693602692</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>-2.159999999999997</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-0.03501945525291827</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0.7400000000000002</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0.344186046511628</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3.150000000000006</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.05588078765300697</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK47" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
